--- a/data/11_systems_waterways_governance.xlsx
+++ b/data/11_systems_waterways_governance.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="1" r:id="R09bbde88615042bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Entities" sheetId="2" r:id="R56a84414285c45c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="3" r:id="R7fde95eb4f9d4015"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Port Governance" sheetId="4" r:id="R2eb30baf84f14d13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="5" r:id="R30218cfeec29420a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waterway Systems" sheetId="6" r:id="R8b90ac6db7684285"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locks &amp; Canals" sheetId="7" r:id="Rf47e035e818b4be4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Interfaces" sheetId="8" r:id="R0cb37e24f6804b5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="9" r:id="R606f35cd34dc46d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" r:id="R4a195c7a5b9145a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="11" r:id="Rc6511ea94d2b48b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="1" r:id="R88ec3185571d4828"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Entities" sheetId="2" r:id="R87d4edf4d32045ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="3" r:id="Rcb7ea6bb38e549ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Port Governance" sheetId="4" r:id="R3b1827b2deee4583"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="5" r:id="Rda606982204d442e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waterway Systems" sheetId="6" r:id="Rcc91c2f4da0e4d17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locks &amp; Canals" sheetId="7" r:id="Rad818ee6bcd045d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Interfaces" sheetId="8" r:id="R289e0b65c33b4d8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="9" r:id="Rda91fa3a03de40aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" r:id="R390c86c5c9e347ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="11" r:id="R9b9e6ae726c944bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -477,6 +477,34 @@
         <x:v>Marine-access infrastructure / rail hinterland</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="str">
+        <x:v>Badagry / Lagos Gateway Development</x:v>
+      </x:c>
+      <x:c r="C13" s="8" t="str">
+        <x:v>Nigeria</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="str">
+        <x:v>Greenfield port / concession-development lifecycle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>Simandou / Morebaya Mine-Rail-Port System</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>Guinea / China</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>Integrated mine-rail-port commodity corridor</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -812,6 +840,62 @@
       </x:c>
       <x:c r="D23" s="8" t="str">
         <x:v>https://splash247.com/genoa-pushes-ahead-with-megaship-access-expansion/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="8" t="str">
+        <x:v>SRC127_SYS_01</x:v>
+      </x:c>
+      <x:c r="B24" s="8" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="str">
+        <x:v>Badagry / APM Terminals exclusive negotiations</x:v>
+      </x:c>
+      <x:c r="D24" s="8" t="str">
+        <x:v>https://splash247.com/maersk-port-arm-lines-up-badagry-as-next-nigerian-gateway/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="8" t="str">
+        <x:v>SRC127_SYS_02</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="str">
+        <x:v>SimFer</x:v>
+      </x:c>
+      <x:c r="C25" s="8" t="str">
+        <x:v>Morebaya port commissioning</x:v>
+      </x:c>
+      <x:c r="D25" s="8" t="str">
+        <x:v>https://simfer-sa.com/en/media-centre/press-releases/simfer-starts-staged-commissioning-of-key-port-infrastructure-at-morebaya/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="8" t="str">
+        <x:v>SRC127_SYS_03</x:v>
+      </x:c>
+      <x:c r="B26" s="8" t="str">
+        <x:v>SimFer</x:v>
+      </x:c>
+      <x:c r="C26" s="8" t="str">
+        <x:v>Q2 2026 rail spur / port progress</x:v>
+      </x:c>
+      <x:c r="D26" s="8" t="str">
+        <x:v>https://simfer-sa.com/en/media-centre/press-releases/simfer-provides-an-update-on-the-progress-of-the-simandou-project-q2-2026/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="8" t="str">
+        <x:v>SRC127_SYS_04</x:v>
+      </x:c>
+      <x:c r="B27" s="8" t="str">
+        <x:v>SimFer</x:v>
+      </x:c>
+      <x:c r="C27" s="8" t="str">
+        <x:v>First SimFer ore to Dalian</x:v>
+      </x:c>
+      <x:c r="D27" s="8" t="str">
+        <x:v>https://simfer-sa.com/en/media-centre/press-releases/simfers-first-iron-ore-reaches-the-port-of-dalian-in-china/</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2438,6 +2522,210 @@
         <x:v>Genoa-to-Central/Northern Europe corridor</x:v>
       </x:c>
     </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B86" s="8" t="str">
+        <x:v>COMP_APMT</x:v>
+      </x:c>
+      <x:c r="C86" s="8" t="str">
+        <x:v>APM Terminals</x:v>
+      </x:c>
+      <x:c r="D86" s="8" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E86" s="8" t="str">
+        <x:v>Prospective developer/operator under exclusive negotiations</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B87" s="8" t="str">
+        <x:v>COMP_BADAGRY_PORT_DEV</x:v>
+      </x:c>
+      <x:c r="C87" s="8" t="str">
+        <x:v>Badagry Port Development</x:v>
+      </x:c>
+      <x:c r="D87" s="8" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E87" s="8" t="str">
+        <x:v>Project developer / negotiation counterparty</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B88" s="8" t="str">
+        <x:v>PORT_BADAGRY</x:v>
+      </x:c>
+      <x:c r="C88" s="8" t="str">
+        <x:v>Badagry Deep Sea Port</x:v>
+      </x:c>
+      <x:c r="D88" s="8" t="str">
+        <x:v>Port project</x:v>
+      </x:c>
+      <x:c r="E88" s="8" t="str">
+        <x:v>Greenfield deep-sea port west of Lagos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B89" s="8" t="str">
+        <x:v>TERM_APAPA</x:v>
+      </x:c>
+      <x:c r="C89" s="8" t="str">
+        <x:v>Apapa Container Terminal</x:v>
+      </x:c>
+      <x:c r="D89" s="8" t="str">
+        <x:v>Container terminal</x:v>
+      </x:c>
+      <x:c r="E89" s="8" t="str">
+        <x:v>Existing APM Terminals Lagos gateway</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B90" s="8" t="str">
+        <x:v>TERM_ONNE_WACT</x:v>
+      </x:c>
+      <x:c r="C90" s="8" t="str">
+        <x:v>West Africa Container Terminal - Onne</x:v>
+      </x:c>
+      <x:c r="D90" s="8" t="str">
+        <x:v>Container terminal</x:v>
+      </x:c>
+      <x:c r="E90" s="8" t="str">
+        <x:v>Existing APM Terminals Nigeria gateway</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B91" s="8" t="str">
+        <x:v>COMP_SIMFER</x:v>
+      </x:c>
+      <x:c r="C91" s="8" t="str">
+        <x:v>SimFer</x:v>
+      </x:c>
+      <x:c r="D91" s="8" t="str">
+        <x:v>JV / company</x:v>
+      </x:c>
+      <x:c r="E91" s="8" t="str">
+        <x:v>Integrated mine-rail-port developer/operator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B92" s="8" t="str">
+        <x:v>ASSET_SIMFER_MINE</x:v>
+      </x:c>
+      <x:c r="C92" s="8" t="str">
+        <x:v>SimFer Mine - Simandou Blocks 3 &amp; 4</x:v>
+      </x:c>
+      <x:c r="D92" s="8" t="str">
+        <x:v>Mine</x:v>
+      </x:c>
+      <x:c r="E92" s="8" t="str">
+        <x:v>Iron ore production system</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B93" s="8" t="str">
+        <x:v>RAIL_SIMFER_SPUR</x:v>
+      </x:c>
+      <x:c r="C93" s="8" t="str">
+        <x:v>SimFer 70 km Rail Spur</x:v>
+      </x:c>
+      <x:c r="D93" s="8" t="str">
+        <x:v>Rail infrastructure</x:v>
+      </x:c>
+      <x:c r="E93" s="8" t="str">
+        <x:v>Connects mine to Transguinean main line</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B94" s="8" t="str">
+        <x:v>RAIL_TRANSGUINEAN</x:v>
+      </x:c>
+      <x:c r="C94" s="8" t="str">
+        <x:v>Transguinean Main Rail Line</x:v>
+      </x:c>
+      <x:c r="D94" s="8" t="str">
+        <x:v>Rail corridor</x:v>
+      </x:c>
+      <x:c r="E94" s="8" t="str">
+        <x:v>Shared rail export backbone</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B95" s="8" t="str">
+        <x:v>PORT_MOREBAYA</x:v>
+      </x:c>
+      <x:c r="C95" s="8" t="str">
+        <x:v>SimFer Morebaya Port</x:v>
+      </x:c>
+      <x:c r="D95" s="8" t="str">
+        <x:v>Port / export terminal</x:v>
+      </x:c>
+      <x:c r="E95" s="8" t="str">
+        <x:v>SimFer export port under commissioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B96" s="8" t="str">
+        <x:v>PORT_WCS_MOREBAYA</x:v>
+      </x:c>
+      <x:c r="C96" s="8" t="str">
+        <x:v>Winning Consortium Simandou Port</x:v>
+      </x:c>
+      <x:c r="D96" s="8" t="str">
+        <x:v>Port / export terminal</x:v>
+      </x:c>
+      <x:c r="E96" s="8" t="str">
+        <x:v>Interim/current export gateway while SimFer port commissioning continues</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B97" s="8" t="str">
+        <x:v>PORT_DALIAN</x:v>
+      </x:c>
+      <x:c r="C97" s="8" t="str">
+        <x:v>Port of Dalian</x:v>
+      </x:c>
+      <x:c r="D97" s="8" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E97" s="8" t="str">
+        <x:v>Chinese receiving / processing gateway in sample trade route</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3487,6 +3775,160 @@
       </x:c>
       <x:c r="D74" s="8" t="str">
         <x:v>CORR_RHINE_ALPINE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B75" s="8" t="str">
+        <x:v>COMP_APMT</x:v>
+      </x:c>
+      <x:c r="C75" s="8" t="str">
+        <x:v>EXCLUSIVE_NEGOTIATIONS_FOR</x:v>
+      </x:c>
+      <x:c r="D75" s="8" t="str">
+        <x:v>PORT_BADAGRY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B76" s="8" t="str">
+        <x:v>COMP_BADAGRY_PORT_DEV</x:v>
+      </x:c>
+      <x:c r="C76" s="8" t="str">
+        <x:v>DEVELOPS</x:v>
+      </x:c>
+      <x:c r="D76" s="8" t="str">
+        <x:v>PORT_BADAGRY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B77" s="8" t="str">
+        <x:v>COMP_APMT</x:v>
+      </x:c>
+      <x:c r="C77" s="8" t="str">
+        <x:v>OPERATES</x:v>
+      </x:c>
+      <x:c r="D77" s="8" t="str">
+        <x:v>TERM_APAPA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B78" s="8" t="str">
+        <x:v>COMP_APMT</x:v>
+      </x:c>
+      <x:c r="C78" s="8" t="str">
+        <x:v>OPERATES</x:v>
+      </x:c>
+      <x:c r="D78" s="8" t="str">
+        <x:v>TERM_ONNE_WACT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B79" s="8" t="str">
+        <x:v>COMP_SIMFER</x:v>
+      </x:c>
+      <x:c r="C79" s="8" t="str">
+        <x:v>OPERATES_DEVELOPS</x:v>
+      </x:c>
+      <x:c r="D79" s="8" t="str">
+        <x:v>ASSET_SIMFER_MINE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B80" s="8" t="str">
+        <x:v>ASSET_SIMFER_MINE</x:v>
+      </x:c>
+      <x:c r="C80" s="8" t="str">
+        <x:v>RAIL_CONNECTED_TO</x:v>
+      </x:c>
+      <x:c r="D80" s="8" t="str">
+        <x:v>RAIL_SIMFER_SPUR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B81" s="8" t="str">
+        <x:v>RAIL_SIMFER_SPUR</x:v>
+      </x:c>
+      <x:c r="C81" s="8" t="str">
+        <x:v>CONNECTS_TO</x:v>
+      </x:c>
+      <x:c r="D81" s="8" t="str">
+        <x:v>RAIL_TRANSGUINEAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B82" s="8" t="str">
+        <x:v>RAIL_TRANSGUINEAN</x:v>
+      </x:c>
+      <x:c r="C82" s="8" t="str">
+        <x:v>SERVES</x:v>
+      </x:c>
+      <x:c r="D82" s="8" t="str">
+        <x:v>PORT_MOREBAYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B83" s="8" t="str">
+        <x:v>COMP_SIMFER</x:v>
+      </x:c>
+      <x:c r="C83" s="8" t="str">
+        <x:v>COMMISSIONING</x:v>
+      </x:c>
+      <x:c r="D83" s="8" t="str">
+        <x:v>PORT_MOREBAYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B84" s="8" t="str">
+        <x:v>ASSET_SIMFER_MINE</x:v>
+      </x:c>
+      <x:c r="C84" s="8" t="str">
+        <x:v>TEMPORARILY_EXPORTS_THROUGH</x:v>
+      </x:c>
+      <x:c r="D84" s="8" t="str">
+        <x:v>PORT_WCS_MOREBAYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B85" s="8" t="str">
+        <x:v>PORT_MOREBAYA</x:v>
+      </x:c>
+      <x:c r="C85" s="8" t="str">
+        <x:v>EXPORT_ROUTE_TO</x:v>
+      </x:c>
+      <x:c r="D85" s="8" t="str">
+        <x:v>PORT_DALIAN</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4152,6 +4594,126 @@
         <x:v>Under construction</x:v>
       </x:c>
     </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B24" s="8" t="str">
+        <x:v>PORT_BADAGRY</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="str">
+        <x:v>Initial container quay</x:v>
+      </x:c>
+      <x:c r="D24" s="8" t="str">
+        <x:v>Quay</x:v>
+      </x:c>
+      <x:c r="E24" s="8" t="str">
+        <x:v>~740 m planned</x:v>
+      </x:c>
+      <x:c r="F24" s="8" t="str">
+        <x:v>Proposed / negotiation-stage seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="str">
+        <x:v>PORT_BADAGRY</x:v>
+      </x:c>
+      <x:c r="C25" s="8" t="str">
+        <x:v>Deepwater access</x:v>
+      </x:c>
+      <x:c r="D25" s="8" t="str">
+        <x:v>Navigation / berth depth</x:v>
+      </x:c>
+      <x:c r="E25" s="8" t="str">
+        <x:v>~18 m design target</x:v>
+      </x:c>
+      <x:c r="F25" s="8" t="str">
+        <x:v>Proposed / negotiation-stage seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B26" s="8" t="str">
+        <x:v>PORT_MOREBAYA</x:v>
+      </x:c>
+      <x:c r="C26" s="8" t="str">
+        <x:v>Stockyard systems</x:v>
+      </x:c>
+      <x:c r="D26" s="8" t="str">
+        <x:v>Bulk handling</x:v>
+      </x:c>
+      <x:c r="E26" s="8" t="str">
+        <x:v>Iron ore storage / transfer</x:v>
+      </x:c>
+      <x:c r="F26" s="8" t="str">
+        <x:v>Commissioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B27" s="8" t="str">
+        <x:v>PORT_MOREBAYA</x:v>
+      </x:c>
+      <x:c r="C27" s="8" t="str">
+        <x:v>Stacker-reclaimers</x:v>
+      </x:c>
+      <x:c r="D27" s="8" t="str">
+        <x:v>Bulk handling equipment</x:v>
+      </x:c>
+      <x:c r="E27" s="8" t="str">
+        <x:v>Ore stacking / reclaiming</x:v>
+      </x:c>
+      <x:c r="F27" s="8" t="str">
+        <x:v>Commissioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B28" s="8" t="str">
+        <x:v>PORT_MOREBAYA</x:v>
+      </x:c>
+      <x:c r="C28" s="8" t="str">
+        <x:v>Shiploaders</x:v>
+      </x:c>
+      <x:c r="D28" s="8" t="str">
+        <x:v>Marine loading equipment</x:v>
+      </x:c>
+      <x:c r="E28" s="8" t="str">
+        <x:v>3 shiploaders reported arrived by Q2 2026</x:v>
+      </x:c>
+      <x:c r="F28" s="8" t="str">
+        <x:v>Commissioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B29" s="8" t="str">
+        <x:v>RAIL_SIMFER_SPUR</x:v>
+      </x:c>
+      <x:c r="C29" s="8" t="str">
+        <x:v>Mine rail spur</x:v>
+      </x:c>
+      <x:c r="D29" s="8" t="str">
+        <x:v>Rail line</x:v>
+      </x:c>
+      <x:c r="E29" s="8" t="str">
+        <x:v>70 km</x:v>
+      </x:c>
+      <x:c r="F29" s="8" t="str">
+        <x:v>Operational</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4801,6 +5363,74 @@
         <x:v>Links Ligurian gateway to European hinterland</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="B18" s="8" t="str">
+        <x:v>PORT_BADAGRY</x:v>
+      </x:c>
+      <x:c r="C18" s="8" t="str">
+        <x:v>MARITIME / ROAD</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="str">
+        <x:v>West African liner network / Lagos hinterland</x:v>
+      </x:c>
+      <x:c r="E18" s="8" t="str">
+        <x:v>Future deep-sea and transhipment gateway</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B19" s="8" t="str">
+        <x:v>ASSET_SIMFER_MINE</x:v>
+      </x:c>
+      <x:c r="C19" s="8" t="str">
+        <x:v>RAIL</x:v>
+      </x:c>
+      <x:c r="D19" s="8" t="str">
+        <x:v>RAIL_SIMFER_SPUR</x:v>
+      </x:c>
+      <x:c r="E19" s="8" t="str">
+        <x:v>Mine-to-export rail interface</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B20" s="8" t="str">
+        <x:v>PORT_MOREBAYA</x:v>
+      </x:c>
+      <x:c r="C20" s="8" t="str">
+        <x:v>MARITIME</x:v>
+      </x:c>
+      <x:c r="D20" s="8" t="str">
+        <x:v>Atlantic / China bulk route</x:v>
+      </x:c>
+      <x:c r="E20" s="8" t="str">
+        <x:v>Iron ore export</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="B21" s="8" t="str">
+        <x:v>PORT_WCS_MOREBAYA</x:v>
+      </x:c>
+      <x:c r="C21" s="8" t="str">
+        <x:v>MARITIME</x:v>
+      </x:c>
+      <x:c r="D21" s="8" t="str">
+        <x:v>Interim SimFer export route</x:v>
+      </x:c>
+      <x:c r="E21" s="8" t="str">
+        <x:v>Temporary/current gateway</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4947,6 +5577,28 @@
         <x:v>Can marine-access works → megaship capability → port competitiveness → rail-hinterland capacity be traversed as one system?</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="8" t="str">
+        <x:v>TEST_12</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="str">
+        <x:v>SYS_BADAGRY</x:v>
+      </x:c>
+      <x:c r="C13" s="8" t="str">
+        <x:v>Can proposed / exclusive-negotiation / future-operator status remain distinct from current APM assets at Apapa and Onne?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="8" t="str">
+        <x:v>TEST_13</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>SYS_SIMANDOU</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>Can mine → rail spur → shared main line → commissioning port → temporary alternative port → export market be traversed with lifecycle status?</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/11_systems_waterways_governance.xlsx
+++ b/data/11_systems_waterways_governance.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="1" r:id="R88ec3185571d4828"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Entities" sheetId="2" r:id="R87d4edf4d32045ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="3" r:id="Rcb7ea6bb38e549ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Port Governance" sheetId="4" r:id="R3b1827b2deee4583"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="5" r:id="Rda606982204d442e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waterway Systems" sheetId="6" r:id="Rcc91c2f4da0e4d17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locks &amp; Canals" sheetId="7" r:id="Rad818ee6bcd045d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Interfaces" sheetId="8" r:id="R289e0b65c33b4d8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="9" r:id="Rda91fa3a03de40aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" r:id="R390c86c5c9e347ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="11" r:id="R9b9e6ae726c944bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="1" r:id="R6971aacd1bf041a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Entities" sheetId="2" r:id="R4482976bf20649ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="3" r:id="Reb730f8e7d1547dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Port Governance" sheetId="4" r:id="R1a503f0e440d4dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="5" r:id="R63249c7c48bc48b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waterway Systems" sheetId="6" r:id="R65e12987ef744a45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locks &amp; Canals" sheetId="7" r:id="R974a914ba84a4d49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Interfaces" sheetId="8" r:id="Rba512ba51aa947ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="9" r:id="R3b282850567b48ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" r:id="R739f0d86ea6447f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="11" r:id="Rb7904a61d6aa4889"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -505,6 +505,20 @@
         <x:v>Integrated mine-rail-port commodity corridor</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Persian Gulf / Hormuz / Gulf of Oman Security System</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Iran; UAE; Oman; Iraq; Kuwait; Bahrain</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Maritime security / energy chokepoint</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -896,6 +910,48 @@
       </x:c>
       <x:c r="D27" s="8" t="str">
         <x:v>https://simfer-sa.com/en/media-centre/press-releases/simfers-first-iron-ore-reaches-the-port-of-dalian-in-china/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>SRC132_SYS_001</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>U.S. Central Command</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Sept. 8 tanker strikes / Gulf of Oman / Kharg</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>https://www.centcom.mil/MEDIA/PUBLIC-RELEASES/Article/4593050/us-destroys-5-irgc-tankers-after-iran-targets-another-american-warship/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>SRC132_SYS_002</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Sept. 9 commercial shipping attacks / Iraqi waters / Port Rashid</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>https://www.reuters.com/world/europe/several-merchant-vessels-hit-by-disabling-fire-gulf-gulf-oman-2026-09-09/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>SRC132_SYS_003</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>UKMTO</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Regional maritime security advisories</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>https://www.ukmto.org/</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2726,6 +2782,244 @@
         <x:v>Chinese receiving / processing gateway in sample trade route</x:v>
       </x:c>
     </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>WATER_HORMUZ</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>Strait of Hormuz</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>Waterway / chokepoint</x:v>
+      </x:c>
+      <x:c r="E98" t="str">
+        <x:v>Primary transit chokepoint</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>WATER_GULF_OMAN</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>Waterway / sea area</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>Outer Gulf approach / tanker strike area</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>WATER_N_GULF</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>Northern Persian Gulf</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>Waterway / sea area</x:v>
+      </x:c>
+      <x:c r="E100" t="str">
+        <x:v>Iraq / Kuwait / Iran tanker operating area</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>AREA_KHARG</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>Kharg Island / approaches</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>Energy export area</x:v>
+      </x:c>
+      <x:c r="E101" t="str">
+        <x:v>Iranian crude export / tanker concentration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>PORTG0045</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>Mina Rashid</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>Dubai anchorage / port-approach exposure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>PORTG0046</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Fujairah</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>UAE Gulf of Oman gateway / bunkering exposure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>PORTG0071</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Fujairah Port / Fujairah Terminals</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>UAE east-coast logistics gateway</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>PORTG0250</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>Port of Umm Qasr / Basra</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>Iraqi northern-Gulf gateway</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>VES_GULF_RIESCO</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>RIESCO</x:v>
+      </x:c>
+      <x:c r="D106" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E106" t="str">
+        <x:v>CENTCOM-struck tanker</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>VES_GULF_HORIZON1</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>HORIZON 1</x:v>
+      </x:c>
+      <x:c r="D107" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E107" t="str">
+        <x:v>CENTCOM-struck tanker</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>VES_GULF_KAVIZ</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>KAVIZ</x:v>
+      </x:c>
+      <x:c r="D108" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E108" t="str">
+        <x:v>CENTCOM-struck tanker</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>VES_GULF_CHARMINAR</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>CHARMINAR</x:v>
+      </x:c>
+      <x:c r="D109" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E109" t="str">
+        <x:v>CENTCOM-struck / sanctioned tanker</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>VES_GULF_DERYA</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>DERYA</x:v>
+      </x:c>
+      <x:c r="D110" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E110" t="str">
+        <x:v>CENTCOM-struck / NITC / sanctioned tanker</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>VES_GULF_NEW_ANDROS</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>NEW ANDROS</x:v>
+      </x:c>
+      <x:c r="D111" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E111" t="str">
+        <x:v>Drone-struck commercial tanker / floating storage</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3929,6 +4223,202 @@
       </x:c>
       <x:c r="D85" s="8" t="str">
         <x:v>PORT_DALIAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>WATER_HORMUZ</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>CONNECTS</x:v>
+      </x:c>
+      <x:c r="D86" t="str">
+        <x:v>WATER_GULF_OMAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>WATER_HORMUZ</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>CONNECTS</x:v>
+      </x:c>
+      <x:c r="D87" t="str">
+        <x:v>WATER_N_GULF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>AREA_KHARG</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>LOCATED_IN</x:v>
+      </x:c>
+      <x:c r="D88" t="str">
+        <x:v>WATER_N_GULF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>PORTG0046</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>FRONTS</x:v>
+      </x:c>
+      <x:c r="D89" t="str">
+        <x:v>WATER_GULF_OMAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>PORTG0071</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>FRONTS</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>WATER_GULF_OMAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>PORTG0045</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>FRONTS</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>WATER_N_GULF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>PORTG0250</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>FRONTS</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>WATER_N_GULF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>VES_GULF_RIESCO</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>STRUCK_IN</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
+        <x:v>WATER_GULF_OMAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>VES_GULF_HORIZON1</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>STRUCK_IN</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>WATER_GULF_OMAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>VES_GULF_KAVIZ</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>STRUCK_IN</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>WATER_GULF_OMAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>VES_GULF_CHARMINAR</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>STRUCK_IN</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>WATER_GULF_OMAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>VES_GULF_DERYA</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>STRUCK_NEAR</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>AREA_KHARG</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>VES_GULF_NEW_ANDROS</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>STRUCK_IN</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>WATER_N_GULF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>WATER_HORMUZ</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>AFFECTS</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>PORTG0046</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5431,6 +5921,91 @@
         <x:v>Temporary/current gateway</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>WATER_HORMUZ</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>MARITIME</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>Persian Gulf ↔ Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Primary energy / commercial chokepoint</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>PORTG0046</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>BUNKERING / MARITIME</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>UAE east-coast bunkering and diversion node</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>PORTG0071</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>MARITIME / LAND</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>UAE logistics network</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>Alternative gateway outside Strait</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>PORTG0250</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>MARITIME / ROAD</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>Iraqi oil / logistics network</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>Northern Gulf gateway</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>AREA_KHARG</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>ENERGY / MARITIME</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>Iranian crude export system</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>Tanker loading / export concentration</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/11_systems_waterways_governance.xlsx
+++ b/data/11_systems_waterways_governance.xlsx
@@ -2,17 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="1" r:id="R6971aacd1bf041a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Entities" sheetId="2" r:id="R4482976bf20649ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="3" r:id="Reb730f8e7d1547dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Port Governance" sheetId="4" r:id="R1a503f0e440d4dd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="5" r:id="R63249c7c48bc48b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waterway Systems" sheetId="6" r:id="R65e12987ef744a45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locks &amp; Canals" sheetId="7" r:id="R974a914ba84a4d49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Interfaces" sheetId="8" r:id="Rba512ba51aa947ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="9" r:id="R3b282850567b48ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" r:id="R739f0d86ea6447f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="11" r:id="Rb7904a61d6aa4889"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="1" r:id="R96d94ee38b2948cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Entities" sheetId="2" r:id="R916f674a70a746ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="3" r:id="R1d22bb00e1fc4917"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Port Governance" sheetId="4" r:id="R47932c4c72f54602"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="5" r:id="Rb7190609ad18433b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waterway Systems" sheetId="6" r:id="Ra481065b2c2b4d45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locks &amp; Canals" sheetId="7" r:id="R8b007e15864c4897"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Interfaces" sheetId="8" r:id="R66b3baf96b754897"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="9" r:id="R3ab297697bd64f13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" r:id="R3929c5b151854f36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="11" r:id="R75e624f3bd934982"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hormuz Traffic Monthly" sheetId="12" r:id="R55f7db4970094803"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hormuz API Endpoints" sheetId="13" r:id="R45ecea5174bb40ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -46,8 +48,19 @@
       <x:color rgb="FF0B1F33"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF101820"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -64,15 +77,34 @@
         <x:fgColor rgb="FFC5A253"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -101,11 +133,63 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HormuzTrafficMonthlyTable" displayName="HormuzTrafficMonthlyTable" ref="A1:J8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="Record ID"/>
+    <x:tableColumn id="2" name="Month"/>
+    <x:tableColumn id="3" name="Crossings"/>
+    <x:tableColumn id="4" name="Inbound"/>
+    <x:tableColumn id="5" name="Outbound"/>
+    <x:tableColumn id="6" name="Oil Tankers Outbound"/>
+    <x:tableColumn id="7" name="Estimated Oil (M bbl)"/>
+    <x:tableColumn id="8" name="Data Status"/>
+    <x:tableColumn id="9" name="Coverage Caveat"/>
+    <x:tableColumn id="10" name="Source ID"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="HormuzApiEndpointsTable" displayName="HormuzApiEndpointsTable" ref="A1:J9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="Endpoint ID"/>
+    <x:tableColumn id="2" name="Endpoint"/>
+    <x:tableColumn id="3" name="Parameters"/>
+    <x:tableColumn id="4" name="Coverage"/>
+    <x:tableColumn id="5" name="Format"/>
+    <x:tableColumn id="6" name="Refresh Interval"/>
+    <x:tableColumn id="7" name="Authentication"/>
+    <x:tableColumn id="8" name="License"/>
+    <x:tableColumn id="9" name="Source ID"/>
+    <x:tableColumn id="10" name="Notes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1122,6 +1206,586 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF1F4E78"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="48" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="21" t="str">
+        <x:v>Record ID</x:v>
+      </x:c>
+      <x:c r="B1" s="21" t="str">
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="C1" s="21" t="str">
+        <x:v>Crossings</x:v>
+      </x:c>
+      <x:c r="D1" s="21" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="E1" s="21" t="str">
+        <x:v>Outbound</x:v>
+      </x:c>
+      <x:c r="F1" s="21" t="str">
+        <x:v>Oil Tankers Outbound</x:v>
+      </x:c>
+      <x:c r="G1" s="21" t="str">
+        <x:v>Estimated Oil (M bbl)</x:v>
+      </x:c>
+      <x:c r="H1" s="21" t="str">
+        <x:v>Data Status</x:v>
+      </x:c>
+      <x:c r="I1" s="21" t="str">
+        <x:v>Coverage Caveat</x:v>
+      </x:c>
+      <x:c r="J1" s="21" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="25" t="str">
+        <x:v>HMX_2026_03</x:v>
+      </x:c>
+      <x:c r="B2" s="25" t="str">
+        <x:v>2026-03</x:v>
+      </x:c>
+      <x:c r="C2" s="25" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D2" s="25" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E2" s="25" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F2" s="25" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G2" s="25" t="n">
+        <x:v>15.9</x:v>
+      </x:c>
+      <x:c r="H2" s="25" t="str">
+        <x:v>Partial start month</x:v>
+      </x:c>
+      <x:c r="I2" s="25" t="str">
+        <x:v>Monitoring began 8 March; wartime AIS disruption</x:v>
+      </x:c>
+      <x:c r="J2" s="25" t="str">
+        <x:v>SRC134_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="25" t="str">
+        <x:v>HMX_2026_04</x:v>
+      </x:c>
+      <x:c r="B3" s="25" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="C3" s="25" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="D3" s="25" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="E3" s="25" t="n">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F3" s="25" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G3" s="25" t="n">
+        <x:v>34.1</x:v>
+      </x:c>
+      <x:c r="H3" s="25" t="str">
+        <x:v>Complete month / conservative</x:v>
+      </x:c>
+      <x:c r="I3" s="25" t="str">
+        <x:v>Upstream AIS gaps depress counts</x:v>
+      </x:c>
+      <x:c r="J3" s="25" t="str">
+        <x:v>SRC134_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="25" t="str">
+        <x:v>HMX_2026_05</x:v>
+      </x:c>
+      <x:c r="B4" s="25" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="C4" s="25" t="n">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="D4" s="25" t="n">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="E4" s="25" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F4" s="25" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G4" s="25" t="n">
+        <x:v>34.9</x:v>
+      </x:c>
+      <x:c r="H4" s="25" t="str">
+        <x:v>Complete month / conservative</x:v>
+      </x:c>
+      <x:c r="I4" s="25" t="str">
+        <x:v>Upstream AIS gaps depress counts</x:v>
+      </x:c>
+      <x:c r="J4" s="25" t="str">
+        <x:v>SRC134_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="25" t="str">
+        <x:v>HMX_2026_06</x:v>
+      </x:c>
+      <x:c r="B5" s="25" t="str">
+        <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="C5" s="25" t="n">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="D5" s="25" t="n">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="E5" s="25" t="n">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="F5" s="25" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G5" s="25" t="n">
+        <x:v>82.8</x:v>
+      </x:c>
+      <x:c r="H5" s="25" t="str">
+        <x:v>Complete month / conservative</x:v>
+      </x:c>
+      <x:c r="I5" s="25" t="str">
+        <x:v>Upstream AIS gaps depress counts</x:v>
+      </x:c>
+      <x:c r="J5" s="25" t="str">
+        <x:v>SRC134_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="25" t="str">
+        <x:v>HMX_2026_07</x:v>
+      </x:c>
+      <x:c r="B6" s="25" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="C6" s="25" t="n">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="D6" s="25" t="n">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="E6" s="25" t="n">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="F6" s="25" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G6" s="25" t="n">
+        <x:v>114.7</x:v>
+      </x:c>
+      <x:c r="H6" s="25" t="str">
+        <x:v>Complete month / mixed coverage</x:v>
+      </x:c>
+      <x:c r="I6" s="25" t="str">
+        <x:v>Pre-late-July upstream AIS gap</x:v>
+      </x:c>
+      <x:c r="J6" s="25" t="str">
+        <x:v>SRC134_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="25" t="str">
+        <x:v>HMX_2026_08</x:v>
+      </x:c>
+      <x:c r="B7" s="25" t="str">
+        <x:v>2026-08</x:v>
+      </x:c>
+      <x:c r="C7" s="25" t="n">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="D7" s="25" t="n">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="E7" s="25" t="n">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="F7" s="25" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G7" s="25" t="n">
+        <x:v>55.7</x:v>
+      </x:c>
+      <x:c r="H7" s="25" t="str">
+        <x:v>Complete month</x:v>
+      </x:c>
+      <x:c r="I7" s="25" t="str">
+        <x:v>AIS remains a conservative lower bound</x:v>
+      </x:c>
+      <x:c r="J7" s="25" t="str">
+        <x:v>SRC134_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="25" t="str">
+        <x:v>HMX_2026_09</x:v>
+      </x:c>
+      <x:c r="B8" s="25" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="C8" s="25" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D8" s="25" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E8" s="25" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F8" s="25" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G8" s="25" t="n">
+        <x:v>14.9</x:v>
+      </x:c>
+      <x:c r="H8" s="25" t="str">
+        <x:v>Current month / partial</x:v>
+      </x:c>
+      <x:c r="I8" s="25" t="str">
+        <x:v>Do not compare as a completed month</x:v>
+      </x:c>
+      <x:c r="J8" s="25" t="str">
+        <x:v>SRC134_001</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7f2386f8f754163"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF1F4E78"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="46" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="21" t="str">
+        <x:v>Endpoint ID</x:v>
+      </x:c>
+      <x:c r="B1" s="21" t="str">
+        <x:v>Endpoint</x:v>
+      </x:c>
+      <x:c r="C1" s="21" t="str">
+        <x:v>Parameters</x:v>
+      </x:c>
+      <x:c r="D1" s="21" t="str">
+        <x:v>Coverage</x:v>
+      </x:c>
+      <x:c r="E1" s="21" t="str">
+        <x:v>Format</x:v>
+      </x:c>
+      <x:c r="F1" s="21" t="str">
+        <x:v>Refresh Interval</x:v>
+      </x:c>
+      <x:c r="G1" s="21" t="str">
+        <x:v>Authentication</x:v>
+      </x:c>
+      <x:c r="H1" s="21" t="str">
+        <x:v>License</x:v>
+      </x:c>
+      <x:c r="I1" s="21" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="J1" s="21" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="25" t="str">
+        <x:v>HAPI_001</x:v>
+      </x:c>
+      <x:c r="B2" s="25" t="str">
+        <x:v>/api/summary</x:v>
+      </x:c>
+      <x:c r="C2" s="25" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="D2" s="25" t="str">
+        <x:v>Traffic summary</x:v>
+      </x:c>
+      <x:c r="E2" s="25" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="F2" s="25" t="str">
+        <x:v>30 minutes</x:v>
+      </x:c>
+      <x:c r="G2" s="25" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="H2" s="25" t="str">
+        <x:v>CC BY 4.0</x:v>
+      </x:c>
+      <x:c r="I2" s="25" t="str">
+        <x:v>SRC134_002</x:v>
+      </x:c>
+      <x:c r="J2" s="25" t="str">
+        <x:v>Default 24 hours</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="25" t="str">
+        <x:v>HAPI_002</x:v>
+      </x:c>
+      <x:c r="B3" s="25" t="str">
+        <x:v>/api/crossings</x:v>
+      </x:c>
+      <x:c r="C3" s="25" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="D3" s="25" t="str">
+        <x:v>Individual Strait crossings</x:v>
+      </x:c>
+      <x:c r="E3" s="25" t="str">
+        <x:v>JSON / CSV</x:v>
+      </x:c>
+      <x:c r="F3" s="25" t="str">
+        <x:v>30 minutes</x:v>
+      </x:c>
+      <x:c r="G3" s="25" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="H3" s="25" t="str">
+        <x:v>CC BY 4.0</x:v>
+      </x:c>
+      <x:c r="I3" s="25" t="str">
+        <x:v>SRC134_002</x:v>
+      </x:c>
+      <x:c r="J3" s="25" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="25" t="str">
+        <x:v>HAPI_003</x:v>
+      </x:c>
+      <x:c r="B4" s="25" t="str">
+        <x:v>/api/crossings/by_type</x:v>
+      </x:c>
+      <x:c r="C4" s="25" t="str">
+        <x:v>hours</x:v>
+      </x:c>
+      <x:c r="D4" s="25" t="str">
+        <x:v>Crossings by vessel type</x:v>
+      </x:c>
+      <x:c r="E4" s="25" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="F4" s="25" t="str">
+        <x:v>30 minutes</x:v>
+      </x:c>
+      <x:c r="G4" s="25" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="H4" s="25" t="str">
+        <x:v>CC BY 4.0</x:v>
+      </x:c>
+      <x:c r="I4" s="25" t="str">
+        <x:v>SRC134_002</x:v>
+      </x:c>
+      <x:c r="J4" s="25" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="25" t="str">
+        <x:v>HAPI_004</x:v>
+      </x:c>
+      <x:c r="B5" s="25" t="str">
+        <x:v>/api/crossings/daily</x:v>
+      </x:c>
+      <x:c r="C5" s="25" t="str">
+        <x:v>days</x:v>
+      </x:c>
+      <x:c r="D5" s="25" t="str">
+        <x:v>Daily crossings, up to 90 days</x:v>
+      </x:c>
+      <x:c r="E5" s="25" t="str">
+        <x:v>JSON / CSV</x:v>
+      </x:c>
+      <x:c r="F5" s="25" t="str">
+        <x:v>30 minutes</x:v>
+      </x:c>
+      <x:c r="G5" s="25" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="H5" s="25" t="str">
+        <x:v>CC BY 4.0</x:v>
+      </x:c>
+      <x:c r="I5" s="25" t="str">
+        <x:v>SRC134_002</x:v>
+      </x:c>
+      <x:c r="J5" s="25" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="25" t="str">
+        <x:v>HAPI_005</x:v>
+      </x:c>
+      <x:c r="B6" s="25" t="str">
+        <x:v>/api/ships</x:v>
+      </x:c>
+      <x:c r="C6" s="25" t="str"/>
+      <x:c r="D6" s="25" t="str">
+        <x:v>Current monitored ships</x:v>
+      </x:c>
+      <x:c r="E6" s="25" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="F6" s="25" t="str">
+        <x:v>30 minutes</x:v>
+      </x:c>
+      <x:c r="G6" s="25" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="H6" s="25" t="str">
+        <x:v>CC BY 4.0</x:v>
+      </x:c>
+      <x:c r="I6" s="25" t="str">
+        <x:v>SRC134_002</x:v>
+      </x:c>
+      <x:c r="J6" s="25" t="str">
+        <x:v>About 950 ships per poll stated in docs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="25" t="str">
+        <x:v>HAPI_006</x:v>
+      </x:c>
+      <x:c r="B7" s="25" t="str">
+        <x:v>/api/ships/by_zone</x:v>
+      </x:c>
+      <x:c r="C7" s="25" t="str"/>
+      <x:c r="D7" s="25" t="str">
+        <x:v>Ships grouped by Persian Gulf / Gulf of Oman zones</x:v>
+      </x:c>
+      <x:c r="E7" s="25" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="F7" s="25" t="str">
+        <x:v>30 minutes</x:v>
+      </x:c>
+      <x:c r="G7" s="25" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="H7" s="25" t="str">
+        <x:v>CC BY 4.0</x:v>
+      </x:c>
+      <x:c r="I7" s="25" t="str">
+        <x:v>SRC134_002</x:v>
+      </x:c>
+      <x:c r="J7" s="25" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="25" t="str">
+        <x:v>HAPI_007</x:v>
+      </x:c>
+      <x:c r="B8" s="25" t="str">
+        <x:v>/api/ships/directory</x:v>
+      </x:c>
+      <x:c r="C8" s="25" t="str"/>
+      <x:c r="D8" s="25" t="str">
+        <x:v>Tracked ship directory</x:v>
+      </x:c>
+      <x:c r="E8" s="25" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="F8" s="25" t="str">
+        <x:v>30 minutes</x:v>
+      </x:c>
+      <x:c r="G8" s="25" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="H8" s="25" t="str">
+        <x:v>CC BY 4.0</x:v>
+      </x:c>
+      <x:c r="I8" s="25" t="str">
+        <x:v>SRC134_002</x:v>
+      </x:c>
+      <x:c r="J8" s="25" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="25" t="str">
+        <x:v>HAPI_008</x:v>
+      </x:c>
+      <x:c r="B9" s="25" t="str">
+        <x:v>/api/ships/daily</x:v>
+      </x:c>
+      <x:c r="C9" s="25" t="str">
+        <x:v>days</x:v>
+      </x:c>
+      <x:c r="D9" s="25" t="str">
+        <x:v>Daily ship counts, up to 90 days</x:v>
+      </x:c>
+      <x:c r="E9" s="25" t="str">
+        <x:v>JSON / CSV</x:v>
+      </x:c>
+      <x:c r="F9" s="25" t="str">
+        <x:v>30 minutes</x:v>
+      </x:c>
+      <x:c r="G9" s="25" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="H9" s="25" t="str">
+        <x:v>CC BY 4.0</x:v>
+      </x:c>
+      <x:c r="I9" s="25" t="str">
+        <x:v>SRC134_002</x:v>
+      </x:c>
+      <x:c r="J9" s="25" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb77045246fe64c7b"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>

--- a/data/11_systems_waterways_governance.xlsx
+++ b/data/11_systems_waterways_governance.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="1" r:id="R96d94ee38b2948cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Entities" sheetId="2" r:id="R916f674a70a746ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="3" r:id="R1d22bb00e1fc4917"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Port Governance" sheetId="4" r:id="R47932c4c72f54602"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="5" r:id="Rb7190609ad18433b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waterway Systems" sheetId="6" r:id="Ra481065b2c2b4d45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locks &amp; Canals" sheetId="7" r:id="R8b007e15864c4897"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Interfaces" sheetId="8" r:id="R66b3baf96b754897"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="9" r:id="R3ab297697bd64f13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" r:id="R3929c5b151854f36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="11" r:id="R75e624f3bd934982"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hormuz Traffic Monthly" sheetId="12" r:id="R55f7db4970094803"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hormuz API Endpoints" sheetId="13" r:id="R45ecea5174bb40ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="1" r:id="Rd0c5ec0ab99e439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Entities" sheetId="2" r:id="R256d648316c14196"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Links" sheetId="3" r:id="R992989fea99b4282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Port Governance" sheetId="4" r:id="Re956e4e44df84679"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="5" r:id="R39877bb0f1194544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Waterway Systems" sheetId="6" r:id="Rfb89ce4756bb4807"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locks &amp; Canals" sheetId="7" r:id="R1b88f7b017b441be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Interfaces" sheetId="8" r:id="R5720dc0ab3934648"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="9" r:id="R04457ed15d9b4526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" r:id="R27401eb629274ada"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="11" r:id="Rde69949909164849"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hormuz Traffic Monthly" sheetId="12" r:id="R1fe6e160abb64144"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hormuz API Endpoints" sheetId="13" r:id="Rac19e87cb1b74c86"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1484,7 +1484,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7f2386f8f754163"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a0afb7984154d9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1781,7 +1781,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb77045246fe64c7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82e6cecaf8204ac3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5270,6 +5270,66 @@
       <x:c r="E10" s="8" t="str">
         <x:v>https://www.portsofgenoa.com/it/nuova-diga-foranea-di-genova/il-progetto.html</x:v>
       </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="8" t="str">
+        <x:v>PORTG0015</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="str">
+        <x:v>COMP_BUSAN_PA</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="str">
+        <x:v>PORT AUTHORITY</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>State-owned authority responsible for port governance and operations at Busan.</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="8" t="str">
+        <x:v>PORTG0225</x:v>
+      </x:c>
+      <x:c r="B12" s="8" t="str">
+        <x:v>COMP_BUSAN_PA</x:v>
+      </x:c>
+      <x:c r="C12" s="8" t="str">
+        <x:v>PORT AUTHORITY</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="str">
+        <x:v>State-owned authority responsible for port governance and operations at Port of Busan.</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="8" t="str">
+        <x:v>PORTG0224</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="str">
+        <x:v>COMP_INCHEON_PA</x:v>
+      </x:c>
+      <x:c r="C13" s="8" t="str">
+        <x:v>PORT AUTHORITY</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="str">
+        <x:v>State-owned authority responsible for port governance and operations at Port of Incheon.</x:v>
+      </x:c>
+      <x:c r="E13" s="8" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="8" t="str">
+        <x:v>PORTG0266</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>COMP_YEOSU_GWANGYANG_PA</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>PORT AUTHORITY</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>State-owned authority responsible for port governance and operations at Port of Gwangyang.</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
